--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T09:04:56+00:00</t>
+    <t>2024-02-19T13:34:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T13:34:28+00:00</t>
+    <t>2024-02-19T13:42:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T13:42:29+00:00</t>
+    <t>2024-03-04T16:55:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-04T16:55:03+00:00</t>
+    <t>2024-03-05T15:34:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-05T15:34:40+00:00</t>
+    <t>2024-03-06T10:45:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-06T10:45:14+00:00</t>
+    <t>2024-03-07T10:27:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-07T10:27:01+00:00</t>
+    <t>2024-03-12T12:54:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T12:54:34+00:00</t>
+    <t>2024-03-12T13:20:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T13:20:54+00:00</t>
+    <t>2024-03-12T13:39:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T13:39:01+00:00</t>
+    <t>2024-03-12T13:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T13:58:30+00:00</t>
+    <t>2024-03-12T14:02:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:02:45+00:00</t>
+    <t>2024-03-12T14:08:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:08:02+00:00</t>
+    <t>2024-03-12T14:13:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:13:18+00:00</t>
+    <t>2024-03-12T14:29:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:29:58+00:00</t>
+    <t>2024-03-12T16:57:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T16:57:02+00:00</t>
+    <t>2024-03-12T17:28:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T17:28:16+00:00</t>
+    <t>2024-03-13T08:21:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,13 +57,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-13T08:21:45+00:00</t>
+    <t>2024-03-13T15:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>ANS</t>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
   </si>
   <si>
     <t>Contact</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-13T15:21:15+00:00</t>
+    <t>2024-03-13T15:40:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-13T15:40:01+00:00</t>
+    <t>2024-03-15T14:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-02T13:53:07+00:00</t>
+    <t>2024-04-02T14:01:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0-ballot-4</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-02T14:01:28+00:00</t>
+    <t>2024-04-03T13:55:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T12:41:20+00:00</t>
+    <t>2024-04-08T12:53:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T12:53:48+00:00</t>
+    <t>2024-04-09T07:46:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -325,9 +325,6 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>Extension.extension:academicDegree</t>
   </si>
   <si>
@@ -372,6 +369,9 @@
   </si>
   <si>
     <t>Extension.url</t>
+  </si>
+  <si>
+    <t>N/A</t>
   </si>
   <si>
     <t>Extension.extension:academicDegree.value[x]</t>
@@ -1219,24 +1219,24 @@
         <v>78</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B5" t="s" s="2">
         <v>91</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>76</v>
@@ -1261,10 +1261,10 @@
         <v>93</v>
       </c>
       <c r="L5" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="M5" t="s" s="2">
         <v>104</v>
-      </c>
-      <c r="M5" t="s" s="2">
-        <v>105</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1324,7 +1324,7 @@
         <v>78</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AJ5" t="s" s="2">
         <v>83</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1438,10 +1438,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>108</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>109</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1470,7 +1470,7 @@
         <v>30</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1530,7 +1530,7 @@
         <v>78</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AJ7" t="s" s="2">
         <v>83</v>
@@ -1541,10 +1541,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>110</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>111</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1567,16 +1567,16 @@
         <v>76</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="S8" t="s" s="2">
         <v>76</v>
@@ -1626,22 +1626,22 @@
         <v>76</v>
       </c>
       <c r="AF8" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK8" t="s" s="2">
         <v>116</v>
-      </c>
-      <c r="AG8" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH8" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI8" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ8" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK8" t="s" s="2">
-        <v>101</v>
       </c>
     </row>
     <row r="9">
@@ -1736,13 +1736,13 @@
         <v>85</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AJ9" t="s" s="2">
         <v>125</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>101</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10">
@@ -1781,7 +1781,7 @@
         <v>128</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1841,7 +1841,7 @@
         <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>83</v>
@@ -1855,7 +1855,7 @@
         <v>129</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1958,7 +1958,7 @@
         <v>130</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1987,7 +1987,7 @@
         <v>30</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2047,7 +2047,7 @@
         <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>83</v>
@@ -2061,7 +2061,7 @@
         <v>131</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2084,16 +2084,16 @@
         <v>76</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2143,22 +2143,22 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK13" t="s" s="2">
         <v>116</v>
-      </c>
-      <c r="AG13" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK13" t="s" s="2">
-        <v>101</v>
       </c>
     </row>
     <row r="14">
@@ -2253,13 +2253,13 @@
         <v>85</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>125</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>101</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15">
@@ -2298,7 +2298,7 @@
         <v>136</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2358,7 +2358,7 @@
         <v>78</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>83</v>
@@ -2372,7 +2372,7 @@
         <v>137</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2475,7 +2475,7 @@
         <v>138</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2504,7 +2504,7 @@
         <v>30</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2564,7 +2564,7 @@
         <v>78</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>83</v>
@@ -2578,7 +2578,7 @@
         <v>139</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2601,16 +2601,16 @@
         <v>76</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -2660,22 +2660,22 @@
         <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK18" t="s" s="2">
         <v>116</v>
-      </c>
-      <c r="AG18" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH18" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI18" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ18" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK18" t="s" s="2">
-        <v>101</v>
       </c>
     </row>
     <row r="19">
@@ -2770,21 +2770,21 @@
         <v>85</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>125</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>101</v>
+        <v>116</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2807,16 +2807,16 @@
         <v>76</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -2866,22 +2866,22 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK20" t="s" s="2">
         <v>116</v>
-      </c>
-      <c r="AG20" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH20" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI20" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ20" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK20" t="s" s="2">
-        <v>101</v>
       </c>
     </row>
     <row r="21">
@@ -2978,13 +2978,13 @@
         <v>85</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>125</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>101</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-09T07:46:55+00:00</t>
+    <t>2024-04-10T12:18:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -325,6 +325,9 @@
     <t>Element.extension</t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>Extension.extension:academicDegree</t>
   </si>
   <si>
@@ -369,9 +372,6 @@
   </si>
   <si>
     <t>Extension.url</t>
-  </si>
-  <si>
-    <t>N/A</t>
   </si>
   <si>
     <t>Extension.extension:academicDegree.value[x]</t>
@@ -1219,24 +1219,24 @@
         <v>78</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B5" t="s" s="2">
         <v>91</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>76</v>
@@ -1261,10 +1261,10 @@
         <v>93</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1324,7 +1324,7 @@
         <v>78</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AJ5" t="s" s="2">
         <v>83</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1438,10 +1438,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1470,7 +1470,7 @@
         <v>30</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1530,7 +1530,7 @@
         <v>78</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AJ7" t="s" s="2">
         <v>83</v>
@@ -1541,10 +1541,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1567,16 +1567,16 @@
         <v>76</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="S8" t="s" s="2">
         <v>76</v>
@@ -1626,7 +1626,7 @@
         <v>76</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>85</v>
@@ -1641,7 +1641,7 @@
         <v>76</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>116</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9">
@@ -1736,13 +1736,13 @@
         <v>85</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AJ9" t="s" s="2">
         <v>125</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>116</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10">
@@ -1781,7 +1781,7 @@
         <v>128</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1841,7 +1841,7 @@
         <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>83</v>
@@ -1855,7 +1855,7 @@
         <v>129</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1958,7 +1958,7 @@
         <v>130</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1987,7 +1987,7 @@
         <v>30</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2047,7 +2047,7 @@
         <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>83</v>
@@ -2061,7 +2061,7 @@
         <v>131</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2084,16 +2084,16 @@
         <v>76</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2143,7 +2143,7 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>85</v>
@@ -2158,7 +2158,7 @@
         <v>76</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>116</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14">
@@ -2253,13 +2253,13 @@
         <v>85</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>125</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>116</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -2298,7 +2298,7 @@
         <v>136</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2358,7 +2358,7 @@
         <v>78</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>83</v>
@@ -2372,7 +2372,7 @@
         <v>137</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2475,7 +2475,7 @@
         <v>138</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2504,7 +2504,7 @@
         <v>30</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2564,7 +2564,7 @@
         <v>78</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>83</v>
@@ -2578,7 +2578,7 @@
         <v>139</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2601,16 +2601,16 @@
         <v>76</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -2660,7 +2660,7 @@
         <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>85</v>
@@ -2675,7 +2675,7 @@
         <v>76</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>116</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19">
@@ -2770,21 +2770,21 @@
         <v>85</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>125</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>116</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2807,16 +2807,16 @@
         <v>76</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -2866,7 +2866,7 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>85</v>
@@ -2881,7 +2881,7 @@
         <v>76</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>116</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21">
@@ -2978,13 +2978,13 @@
         <v>85</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>125</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>116</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T12:18:24+00:00</t>
+    <t>2024-04-10T12:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -325,9 +325,6 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>Extension.extension:academicDegree</t>
   </si>
   <si>
@@ -372,6 +369,9 @@
   </si>
   <si>
     <t>Extension.url</t>
+  </si>
+  <si>
+    <t>N/A</t>
   </si>
   <si>
     <t>Extension.extension:academicDegree.value[x]</t>
@@ -1219,24 +1219,24 @@
         <v>78</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B5" t="s" s="2">
         <v>91</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>76</v>
@@ -1261,10 +1261,10 @@
         <v>93</v>
       </c>
       <c r="L5" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="M5" t="s" s="2">
         <v>104</v>
-      </c>
-      <c r="M5" t="s" s="2">
-        <v>105</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1324,7 +1324,7 @@
         <v>78</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AJ5" t="s" s="2">
         <v>83</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>106</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>107</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1438,10 +1438,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>108</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>109</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1470,7 +1470,7 @@
         <v>30</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1530,7 +1530,7 @@
         <v>78</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AJ7" t="s" s="2">
         <v>83</v>
@@ -1541,10 +1541,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>110</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>111</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1567,16 +1567,16 @@
         <v>76</v>
       </c>
       <c r="K8" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L8" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="L8" t="s" s="2">
+      <c r="M8" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="S8" t="s" s="2">
         <v>76</v>
@@ -1626,22 +1626,22 @@
         <v>76</v>
       </c>
       <c r="AF8" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH8" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ8" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK8" t="s" s="2">
         <v>116</v>
-      </c>
-      <c r="AG8" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH8" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI8" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ8" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK8" t="s" s="2">
-        <v>101</v>
       </c>
     </row>
     <row r="9">
@@ -1736,13 +1736,13 @@
         <v>85</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AJ9" t="s" s="2">
         <v>125</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>101</v>
+        <v>116</v>
       </c>
     </row>
     <row r="10">
@@ -1781,7 +1781,7 @@
         <v>128</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1841,7 +1841,7 @@
         <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>83</v>
@@ -1855,7 +1855,7 @@
         <v>129</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1958,7 +1958,7 @@
         <v>130</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1987,7 +1987,7 @@
         <v>30</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2047,7 +2047,7 @@
         <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>83</v>
@@ -2061,7 +2061,7 @@
         <v>131</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2084,16 +2084,16 @@
         <v>76</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2143,22 +2143,22 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK13" t="s" s="2">
         <v>116</v>
-      </c>
-      <c r="AG13" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ13" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK13" t="s" s="2">
-        <v>101</v>
       </c>
     </row>
     <row r="14">
@@ -2253,13 +2253,13 @@
         <v>85</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>125</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>101</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15">
@@ -2298,7 +2298,7 @@
         <v>136</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2358,7 +2358,7 @@
         <v>78</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>83</v>
@@ -2372,7 +2372,7 @@
         <v>137</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2475,7 +2475,7 @@
         <v>138</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2504,7 +2504,7 @@
         <v>30</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2564,7 +2564,7 @@
         <v>78</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>83</v>
@@ -2578,7 +2578,7 @@
         <v>139</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2601,16 +2601,16 @@
         <v>76</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -2660,22 +2660,22 @@
         <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG18" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH18" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI18" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ18" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK18" t="s" s="2">
         <v>116</v>
-      </c>
-      <c r="AG18" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH18" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI18" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ18" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK18" t="s" s="2">
-        <v>101</v>
       </c>
     </row>
     <row r="19">
@@ -2770,21 +2770,21 @@
         <v>85</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>125</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>101</v>
+        <v>116</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2807,16 +2807,16 @@
         <v>76</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>113</v>
       </c>
-      <c r="M20" t="s" s="2">
+      <c r="N20" t="s" s="2">
         <v>114</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>115</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -2866,22 +2866,22 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK20" t="s" s="2">
         <v>116</v>
-      </c>
-      <c r="AG20" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AH20" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI20" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ20" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AK20" t="s" s="2">
-        <v>101</v>
       </c>
     </row>
     <row r="21">
@@ -2978,13 +2978,13 @@
         <v>85</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>125</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>101</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:21:45+00:00</t>
+    <t>2024-04-18T13:43:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-18T13:43:00+00:00</t>
+    <t>2024-04-25T11:33:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -325,6 +325,9 @@
     <t>Element.extension</t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>Extension.extension:academicDegree</t>
   </si>
   <si>
@@ -369,9 +372,6 @@
   </si>
   <si>
     <t>Extension.url</t>
-  </si>
-  <si>
-    <t>N/A</t>
   </si>
   <si>
     <t>Extension.extension:academicDegree.value[x]</t>
@@ -1219,24 +1219,24 @@
         <v>78</v>
       </c>
       <c r="AI4" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AJ4" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AK4" t="s" s="2">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B5" t="s" s="2">
         <v>91</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D5" t="s" s="2">
         <v>76</v>
@@ -1261,10 +1261,10 @@
         <v>93</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1324,7 +1324,7 @@
         <v>78</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AJ5" t="s" s="2">
         <v>83</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1438,10 +1438,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1470,7 +1470,7 @@
         <v>30</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1530,7 +1530,7 @@
         <v>78</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AJ7" t="s" s="2">
         <v>83</v>
@@ -1541,10 +1541,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1567,16 +1567,16 @@
         <v>76</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="S8" t="s" s="2">
         <v>76</v>
@@ -1626,7 +1626,7 @@
         <v>76</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>85</v>
@@ -1641,7 +1641,7 @@
         <v>76</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>116</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9">
@@ -1736,13 +1736,13 @@
         <v>85</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AJ9" t="s" s="2">
         <v>125</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>116</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10">
@@ -1781,7 +1781,7 @@
         <v>128</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1841,7 +1841,7 @@
         <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>83</v>
@@ -1855,7 +1855,7 @@
         <v>129</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1958,7 +1958,7 @@
         <v>130</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1987,7 +1987,7 @@
         <v>30</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2047,7 +2047,7 @@
         <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>83</v>
@@ -2061,7 +2061,7 @@
         <v>131</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2084,16 +2084,16 @@
         <v>76</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2143,7 +2143,7 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>85</v>
@@ -2158,7 +2158,7 @@
         <v>76</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>116</v>
+        <v>101</v>
       </c>
     </row>
     <row r="14">
@@ -2253,13 +2253,13 @@
         <v>85</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>125</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>116</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -2298,7 +2298,7 @@
         <v>136</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2358,7 +2358,7 @@
         <v>78</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>83</v>
@@ -2372,7 +2372,7 @@
         <v>137</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2475,7 +2475,7 @@
         <v>138</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2504,7 +2504,7 @@
         <v>30</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2564,7 +2564,7 @@
         <v>78</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>83</v>
@@ -2578,7 +2578,7 @@
         <v>139</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2601,16 +2601,16 @@
         <v>76</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -2660,7 +2660,7 @@
         <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>85</v>
@@ -2675,7 +2675,7 @@
         <v>76</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>116</v>
+        <v>101</v>
       </c>
     </row>
     <row r="19">
@@ -2770,21 +2770,21 @@
         <v>85</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>125</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>116</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2807,16 +2807,16 @@
         <v>76</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -2866,7 +2866,7 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>85</v>
@@ -2881,7 +2881,7 @@
         <v>76</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>116</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21">
@@ -2978,13 +2978,13 @@
         <v>85</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>125</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>116</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:10:14+00:00</t>
+    <t>2024-06-03T16:22:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:22:01+00:00</t>
+    <t>2024-06-03T16:23:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:23:50+00:00</t>
+    <t>2024-06-03T16:30:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:30:34+00:00</t>
+    <t>2024-06-05T12:07:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-05T12:07:44+00:00</t>
+    <t>2024-06-07T15:57:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-07T15:57:22+00:00</t>
+    <t>2024-07-01T19:46:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-01T19:46:33+00:00</t>
+    <t>2024-07-09T08:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T08:44:23+00:00</t>
+    <t>2024-07-10T09:54:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.1</t>
+    <t>1.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T09:54:14+00:00</t>
+    <t>2024-07-10T10:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T10:00:25+00:00</t>
+    <t>2024-07-10T10:02:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T10:02:38+00:00</t>
+    <t>2024-07-10T10:13:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T10:13:33+00:00</t>
+    <t>2024-07-10T12:01:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T12:01:49+00:00</t>
+    <t>2024-07-10T12:37:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T12:37:24+00:00</t>
+    <t>2024-07-10T13:09:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T13:09:17+00:00</t>
+    <t>2024-07-10T13:09:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T13:09:58+00:00</t>
+    <t>2024-07-10T13:27:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T13:27:13+00:00</t>
+    <t>2024-07-11T14:15:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T14:15:05+00:00</t>
+    <t>2024-07-11T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0-snapshot</t>
+    <t>1.1.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T14:20:03+00:00</t>
+    <t>2024-07-11T15:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T15:32:47+00:00</t>
+    <t>2024-07-11T15:43:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T15:43:40+00:00</t>
+    <t>2024-07-11T16:04:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T16:04:15+00:00</t>
+    <t>2024-07-12T06:54:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-12T06:54:28+00:00</t>
+    <t>2024-07-12T07:24:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-27T17:01:01+00:00</t>
+    <t>2025-01-31T09:33:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-31T09:33:18+00:00</t>
+    <t>2025-02-03T16:26:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-03T16:26:04+00:00</t>
+    <t>2025-02-11T12:19:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T12:19:13+00:00</t>
+    <t>2025-02-11T12:46:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T12:46:26+00:00</t>
+    <t>2025-02-11T13:37:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T13:37:59+00:00</t>
+    <t>2025-02-11T14:09:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T14:09:44+00:00</t>
+    <t>2025-02-11T15:57:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T15:57:50+00:00</t>
+    <t>2025-02-11T16:04:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T16:04:30+00:00</t>
+    <t>2025-02-11T16:35:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-17T22:39:20+00:00</t>
+    <t>2025-02-24T08:37:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T08:37:03+00:00</t>
+    <t>2025-02-27T14:21:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T14:21:41+00:00</t>
+    <t>2025-02-27T14:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T14:23:05+00:00</t>
+    <t>2025-02-28T10:02:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T10:02:48+00:00</t>
+    <t>2025-03-05T17:59:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-05T17:59:44+00:00</t>
+    <t>2025-03-06T14:41:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T14:41:30+00:00</t>
+    <t>2025-03-06T14:56:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T14:56:25+00:00</t>
+    <t>2025-03-12T15:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T15:24:25+00:00</t>
+    <t>2025-03-18T14:02:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T14:02:39+00:00</t>
+    <t>2025-03-18T16:59:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T16:59:29+00:00</t>
+    <t>2025-03-21T10:50:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-1</t>
+    <t>1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T12:01:00+00:00</t>
+    <t>2026-06-19T13:53:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T13:53:04+00:00</t>
+    <t>2026-06-19T14:07:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T14:07:56+00:00</t>
+    <t>2026-06-23T09:20:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-23T09:20:47+00:00</t>
+    <t>2026-06-23T12:21:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-23T12:21:55+00:00</t>
+    <t>2026-06-26T10:36:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T10:36:05+00:00</t>
+    <t>2026-06-27T10:35:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-27T10:35:23+00:00</t>
+    <t>2026-06-30T07:59:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="721" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="882" uniqueCount="151">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T07:59:11+00:00</t>
+    <t>2026-07-10T15:33:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -450,6 +450,30 @@
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J88-AnneeUniversitaire-RASS/FHIR/JDV-J88-AnneeUniversitaire-RASS|20251016120000</t>
+  </si>
+  <si>
+    <t>Extension.extension:trainingLocation</t>
+  </si>
+  <si>
+    <t>trainingLocation</t>
+  </si>
+  <si>
+    <t>[Donnée restreinte] : Type de lieu ayant délivré le diplôme (lieuFormation).</t>
+  </si>
+  <si>
+    <t>Extension.extension:trainingLocation.id</t>
+  </si>
+  <si>
+    <t>Extension.extension:trainingLocation.extension</t>
+  </si>
+  <si>
+    <t>Extension.extension:trainingLocation.url</t>
+  </si>
+  <si>
+    <t>Extension.extension:trainingLocation.value[x]</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J235-LieuFormation-EPARS/FHIR/JDV-J235-LieuFormation-EPARS|20240726120000</t>
   </si>
   <si>
     <t>base64Binary
@@ -763,7 +787,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK21"/>
+  <dimension ref="A1:AK26"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="38.86328125" customWidth="true" bestFit="true"/>
@@ -2781,18 +2805,20 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>115</v>
+        <v>142</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="C20" s="2"/>
+        <v>91</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>143</v>
+      </c>
       <c r="D20" t="s" s="2">
         <v>76</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>85</v>
@@ -2807,24 +2833,22 @@
         <v>76</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>112</v>
+        <v>144</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
-        <v>3</v>
+        <v>76</v>
       </c>
       <c r="S20" t="s" s="2">
         <v>76</v>
@@ -2866,30 +2890,30 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>115</v>
+        <v>100</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>116</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2900,7 +2924,7 @@
         <v>77</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>76</v>
@@ -2912,13 +2936,13 @@
         <v>76</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>142</v>
+        <v>86</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>120</v>
+        <v>87</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>121</v>
+        <v>88</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -2969,21 +2993,538 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK21" t="s" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E22" s="2"/>
+      <c r="F22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J22" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K22" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q22" s="2"/>
+      <c r="R22" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S22" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T22" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U22" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X22" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AF22" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AG22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI22" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK22" t="s" s="2">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E23" s="2"/>
+      <c r="F23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K23" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M23" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O23" s="2"/>
+      <c r="P23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q23" s="2"/>
+      <c r="R23" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="S23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF23" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK23" t="s" s="2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E24" s="2"/>
+      <c r="F24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K24" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q24" s="2"/>
+      <c r="R24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X24" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="Y24" s="2"/>
+      <c r="Z24" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF24" t="s" s="2">
         <v>124</v>
       </c>
-      <c r="AG21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AH21" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI21" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AJ21" t="s" s="2">
+      <c r="AG24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
         <v>125</v>
       </c>
-      <c r="AK21" t="s" s="2">
+      <c r="AK24" t="s" s="2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E25" s="2"/>
+      <c r="F25" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="G25" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K25" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N25" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O25" s="2"/>
+      <c r="P25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q25" s="2"/>
+      <c r="R25" t="s" s="2">
+        <v>3</v>
+      </c>
+      <c r="S25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF25" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AK25" t="s" s="2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E26" s="2"/>
+      <c r="F26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K26" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q26" s="2"/>
+      <c r="R26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF26" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="AG26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="AK26" t="s" s="2">
         <v>116</v>
       </c>
     </row>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-2</t>
+    <t>1.2.0-snapshot-3</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T15:33:23+00:00</t>
+    <t>2026-07-10T15:46:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T15:46:03+00:00</t>
+    <t>2026-08-03T13:23:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T13:23:25+00:00</t>
+    <t>2026-08-03T14:28:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T14:28:09+00:00</t>
+    <t>2026-08-04T08:16:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-ext-education-level.xlsx
+++ b/main/ig/StructureDefinition-as-ext-education-level.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T08:16:57+00:00</t>
+    <t>2026-08-04T12:10:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
